--- a/Mantenimiento_UPS_2026.xlsx
+++ b/Mantenimiento_UPS_2026.xlsx
@@ -130,7 +130,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4046" uniqueCount="1076">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4064" uniqueCount="1077">
   <si>
     <t>TIENDA</t>
   </si>
@@ -3391,6 +3391,9 @@
   </si>
   <si>
     <t>KFC115</t>
+  </si>
+  <si>
+    <t>DAÑADO</t>
   </si>
 </sst>
 </file>
@@ -6285,11 +6288,21 @@
       <c r="H41" s="13" t="s">
         <v>363</v>
       </c>
-      <c r="I41" s="14"/>
-      <c r="J41" s="15"/>
-      <c r="K41" s="13"/>
-      <c r="L41" s="13"/>
-      <c r="M41" s="16"/>
+      <c r="I41" s="14">
+        <v>1</v>
+      </c>
+      <c r="J41" s="15">
+        <v>46254</v>
+      </c>
+      <c r="K41" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="L41" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="M41" s="16">
+        <v>0.03</v>
+      </c>
     </row>
     <row r="42" spans="1:13" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A42" s="9">
@@ -8644,11 +8657,21 @@
       <c r="H106" s="13" t="s">
         <v>222</v>
       </c>
-      <c r="I106" s="14"/>
-      <c r="J106" s="15"/>
-      <c r="K106" s="13"/>
-      <c r="L106" s="13"/>
-      <c r="M106" s="16"/>
+      <c r="I106" s="14">
+        <v>1</v>
+      </c>
+      <c r="J106" s="15">
+        <v>46247</v>
+      </c>
+      <c r="K106" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="L106" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="M106" s="16">
+        <v>0.05</v>
+      </c>
     </row>
     <row r="107" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A107" s="9">
@@ -9176,11 +9199,21 @@
       <c r="H120" s="13" t="s">
         <v>249</v>
       </c>
-      <c r="I120" s="14"/>
-      <c r="J120" s="15"/>
-      <c r="K120" s="13"/>
-      <c r="L120" s="13"/>
-      <c r="M120" s="16"/>
+      <c r="I120" s="14">
+        <v>1</v>
+      </c>
+      <c r="J120" s="15">
+        <v>46283</v>
+      </c>
+      <c r="K120" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="L120" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="M120" s="16">
+        <v>0.05</v>
+      </c>
     </row>
     <row r="121" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A121" s="9">
@@ -9207,11 +9240,21 @@
       <c r="H121" s="13" t="s">
         <v>251</v>
       </c>
-      <c r="I121" s="14"/>
-      <c r="J121" s="15"/>
-      <c r="K121" s="13"/>
-      <c r="L121" s="13"/>
-      <c r="M121" s="16"/>
+      <c r="I121" s="14">
+        <v>1</v>
+      </c>
+      <c r="J121" s="15">
+        <v>46274</v>
+      </c>
+      <c r="K121" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="L121" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="M121" s="16">
+        <v>7.0000000000000007E-2</v>
+      </c>
     </row>
     <row r="122" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A122" s="9">
@@ -13554,11 +13597,21 @@
       <c r="H236" s="13" t="s">
         <v>134</v>
       </c>
-      <c r="I236" s="14"/>
-      <c r="J236" s="15"/>
-      <c r="K236" s="13"/>
-      <c r="L236" s="13"/>
-      <c r="M236" s="16"/>
+      <c r="I236" s="14">
+        <v>1</v>
+      </c>
+      <c r="J236" s="15">
+        <v>46251</v>
+      </c>
+      <c r="K236" s="13" t="s">
+        <v>930</v>
+      </c>
+      <c r="L236" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="M236" s="16">
+        <v>0.14000000000000001</v>
+      </c>
     </row>
     <row r="237" spans="1:13" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A237" s="9">
@@ -17580,11 +17633,21 @@
         <v>14</v>
       </c>
       <c r="H344" s="13"/>
-      <c r="I344" s="14"/>
-      <c r="J344" s="15"/>
-      <c r="K344" s="13"/>
-      <c r="L344" s="13"/>
-      <c r="M344" s="16"/>
+      <c r="I344" s="14">
+        <v>1</v>
+      </c>
+      <c r="J344" s="15">
+        <v>46255</v>
+      </c>
+      <c r="K344" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="L344" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="M344" s="16">
+        <v>0</v>
+      </c>
     </row>
     <row r="345" spans="1:13" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A345" s="9">
@@ -18296,11 +18359,21 @@
       <c r="H364" s="13" t="s">
         <v>916</v>
       </c>
-      <c r="I364" s="14"/>
-      <c r="J364" s="13"/>
-      <c r="K364" s="13"/>
-      <c r="L364" s="13"/>
-      <c r="M364" s="18"/>
+      <c r="I364" s="14">
+        <v>1</v>
+      </c>
+      <c r="J364" s="15">
+        <v>46262</v>
+      </c>
+      <c r="K364" s="13" t="s">
+        <v>1076</v>
+      </c>
+      <c r="L364" s="13" t="s">
+        <v>1060</v>
+      </c>
+      <c r="M364" s="16">
+        <v>0.14000000000000001</v>
+      </c>
     </row>
     <row r="365" spans="1:13" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A365" s="9">
@@ -18625,11 +18698,21 @@
       <c r="H373" s="13" t="s">
         <v>882</v>
       </c>
-      <c r="I373" s="14"/>
-      <c r="J373" s="13"/>
-      <c r="K373" s="13"/>
-      <c r="L373" s="13"/>
-      <c r="M373" s="18"/>
+      <c r="I373" s="14">
+        <v>1</v>
+      </c>
+      <c r="J373" s="15">
+        <v>46245</v>
+      </c>
+      <c r="K373" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="L373" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="M373" s="16">
+        <v>0.24</v>
+      </c>
     </row>
     <row r="374" spans="1:13" ht="20.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A374" s="9">
@@ -18701,7 +18784,7 @@
       <c r="J375" s="13"/>
       <c r="K375" s="13"/>
       <c r="L375" s="13"/>
-      <c r="M375" s="18"/>
+      <c r="M375" s="16"/>
     </row>
     <row r="376" spans="1:13" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A376" s="9">
@@ -18732,7 +18815,7 @@
       <c r="J376" s="15"/>
       <c r="K376" s="13"/>
       <c r="L376" s="13"/>
-      <c r="M376" s="18"/>
+      <c r="M376" s="16"/>
     </row>
     <row r="377" spans="1:13" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A377" s="9">
@@ -18763,7 +18846,7 @@
       <c r="J377" s="13"/>
       <c r="K377" s="13"/>
       <c r="L377" s="13"/>
-      <c r="M377" s="18"/>
+      <c r="M377" s="16"/>
     </row>
     <row r="378" spans="1:13" ht="20.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A378" s="9">
@@ -21731,11 +21814,21 @@
       <c r="H457" s="13" t="s">
         <v>768</v>
       </c>
-      <c r="I457" s="14"/>
-      <c r="J457" s="13"/>
-      <c r="K457" s="51"/>
-      <c r="L457" s="13"/>
-      <c r="M457" s="16"/>
+      <c r="I457" s="14">
+        <v>1</v>
+      </c>
+      <c r="J457" s="15">
+        <v>46245</v>
+      </c>
+      <c r="K457" s="51" t="s">
+        <v>42</v>
+      </c>
+      <c r="L457" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="M457" s="16">
+        <v>0.17</v>
+      </c>
     </row>
     <row r="458" spans="1:13" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A458" s="9">
